--- a/Airfix/Airfix_Kits_In_Series_Order.xlsx
+++ b/Airfix/Airfix_Kits_In_Series_Order.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/datamgmt/Documents/GitHub/PlasticModelCatalogues/Airfix/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{25A82F84-8F53-E349-BFC4-AC67785734CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1FC460-C011-344A-802C-CDEB0A15F039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3740" yWindow="1760" windowWidth="41760" windowHeight="23040" xr2:uid="{B7A59F4E-630A-964C-8A59-4B9ABA2B2888}"/>
+    <workbookView xWindow="7500" yWindow="5760" windowWidth="41760" windowHeight="23040" xr2:uid="{B7A59F4E-630A-964C-8A59-4B9ABA2B2888}"/>
   </bookViews>
   <sheets>
     <sheet name="Airfix Kits_In_Series_Order" sheetId="1" r:id="rId1"/>
@@ -10832,24 +10832,6 @@
     <t>Series</t>
   </si>
   <si>
-    <t>Cat 1</t>
-  </si>
-  <si>
-    <t>Cat 2</t>
-  </si>
-  <si>
-    <t>Cat 3</t>
-  </si>
-  <si>
-    <t>Cat 4</t>
-  </si>
-  <si>
-    <t>Cat 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cat 6 </t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
@@ -11043,13 +11025,31 @@
   </si>
   <si>
     <t>Prototype</t>
+  </si>
+  <si>
+    <t>Code 1</t>
+  </si>
+  <si>
+    <t>Code 2</t>
+  </si>
+  <si>
+    <t>Code 3</t>
+  </si>
+  <si>
+    <t>Code 4</t>
+  </si>
+  <si>
+    <t>Code 5</t>
+  </si>
+  <si>
+    <t>Code 6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -11190,6 +11190,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -11533,10 +11539,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -11934,29 +11943,29 @@
       <c r="B1" s="2" t="s">
         <v>3597</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3664</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3665</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>3666</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>3667</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3668</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>3598</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3599</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3600</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>3601</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3602</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>3603</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>3604</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>3665</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -12292,10 +12301,10 @@
         <v>46</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>3607</v>
+        <v>3601</v>
       </c>
       <c r="J25" t="s">
-        <v>3658</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -12309,10 +12318,10 @@
         <v>47</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>3608</v>
+        <v>3602</v>
       </c>
       <c r="J26" t="s">
-        <v>3658</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -12426,10 +12435,10 @@
         <v>66</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>3609</v>
+        <v>3603</v>
       </c>
       <c r="J32" t="s">
-        <v>3666</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
@@ -13895,10 +13904,10 @@
         <v>352</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>3607</v>
+        <v>3601</v>
       </c>
       <c r="J102" t="s">
-        <v>3659</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
@@ -13918,10 +13927,10 @@
         <v>355</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>3610</v>
+        <v>3604</v>
       </c>
       <c r="J103" t="s">
-        <v>3659</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
@@ -13949,10 +13958,10 @@
         <v>358</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>3611</v>
+        <v>3605</v>
       </c>
       <c r="J105" t="s">
-        <v>3660</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.2">
@@ -13966,10 +13975,10 @@
         <v>359</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>3612</v>
+        <v>3606</v>
       </c>
       <c r="J106" t="s">
-        <v>3660</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
@@ -13983,10 +13992,10 @@
         <v>360</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>3613</v>
+        <v>3607</v>
       </c>
       <c r="J107" t="s">
-        <v>3660</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.2">
@@ -14000,10 +14009,10 @@
         <v>361</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>3614</v>
+        <v>3608</v>
       </c>
       <c r="J108" t="s">
-        <v>3660</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.2">
@@ -14017,10 +14026,10 @@
         <v>362</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>3615</v>
+        <v>3609</v>
       </c>
       <c r="J109" t="s">
-        <v>3660</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.2">
@@ -14034,10 +14043,10 @@
         <v>363</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>3616</v>
+        <v>3610</v>
       </c>
       <c r="J110" t="s">
-        <v>3660</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.2">
@@ -14051,10 +14060,10 @@
         <v>364</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>3617</v>
+        <v>3611</v>
       </c>
       <c r="J111" t="s">
-        <v>3660</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.2">
@@ -14068,10 +14077,10 @@
         <v>365</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>3618</v>
+        <v>3612</v>
       </c>
       <c r="J112" t="s">
-        <v>3660</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.2">
@@ -14085,10 +14094,10 @@
         <v>366</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>3619</v>
+        <v>3613</v>
       </c>
       <c r="J113" t="s">
-        <v>3660</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.2">
@@ -15466,10 +15475,10 @@
         <v>610</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>3620</v>
+        <v>3614</v>
       </c>
       <c r="J187" t="s">
-        <v>3659</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.2">
@@ -15486,10 +15495,10 @@
         <v>612</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>3621</v>
+        <v>3615</v>
       </c>
       <c r="J188" t="s">
-        <v>3659</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.2">
@@ -15506,10 +15515,10 @@
         <v>614</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>3622</v>
+        <v>3616</v>
       </c>
       <c r="J189" t="s">
-        <v>3659</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.2">
@@ -15661,10 +15670,10 @@
         <v>633</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>3623</v>
+        <v>3617</v>
       </c>
       <c r="J199" t="s">
-        <v>3661</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.2">
@@ -15678,10 +15687,10 @@
         <v>634</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>3624</v>
+        <v>3618</v>
       </c>
       <c r="J200" t="s">
-        <v>3661</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.2">
@@ -15695,10 +15704,10 @@
         <v>635</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>3625</v>
+        <v>3619</v>
       </c>
       <c r="J201" t="s">
-        <v>3661</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.2">
@@ -15712,10 +15721,10 @@
         <v>636</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>3626</v>
+        <v>3620</v>
       </c>
       <c r="J202" t="s">
-        <v>3661</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.2">
@@ -15729,10 +15738,10 @@
         <v>637</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>3627</v>
+        <v>3621</v>
       </c>
       <c r="J203" t="s">
-        <v>3661</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.2">
@@ -15746,10 +15755,10 @@
         <v>638</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>3628</v>
+        <v>3622</v>
       </c>
       <c r="J204" t="s">
-        <v>3661</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.2">
@@ -15763,10 +15772,10 @@
         <v>639</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>3629</v>
+        <v>3623</v>
       </c>
       <c r="J205" t="s">
-        <v>3661</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.2">
@@ -15780,10 +15789,10 @@
         <v>640</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>3630</v>
+        <v>3624</v>
       </c>
       <c r="J206" t="s">
-        <v>3661</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.2">
@@ -15797,10 +15806,10 @@
         <v>641</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>3631</v>
+        <v>3625</v>
       </c>
       <c r="J207" t="s">
-        <v>3661</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.2">
@@ -15814,10 +15823,10 @@
         <v>642</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>3632</v>
+        <v>3626</v>
       </c>
       <c r="J208" t="s">
-        <v>3661</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.2">
@@ -15831,10 +15840,10 @@
         <v>643</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>3633</v>
+        <v>3627</v>
       </c>
       <c r="J209" t="s">
-        <v>3661</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.2">
@@ -15848,10 +15857,10 @@
         <v>644</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>3634</v>
+        <v>3628</v>
       </c>
       <c r="J210" t="s">
-        <v>3661</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.2">
@@ -15865,10 +15874,10 @@
         <v>645</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>3635</v>
+        <v>3629</v>
       </c>
       <c r="J211" t="s">
-        <v>3661</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.2">
@@ -15882,10 +15891,10 @@
         <v>646</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>3607</v>
+        <v>3601</v>
       </c>
       <c r="J212" t="s">
-        <v>3662</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.2">
@@ -15899,10 +15908,10 @@
         <v>647</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>3636</v>
+        <v>3630</v>
       </c>
       <c r="J213" t="s">
-        <v>3662</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.2">
@@ -16183,10 +16192,10 @@
         <v>694</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>3637</v>
+        <v>3631</v>
       </c>
       <c r="J229" t="s">
-        <v>3668</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.2">
@@ -18269,10 +18278,10 @@
         <v>1041</v>
       </c>
       <c r="I348" s="1" t="s">
-        <v>3638</v>
+        <v>3632</v>
       </c>
       <c r="J348" t="s">
-        <v>3659</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.2">
@@ -18571,7 +18580,7 @@
         <v>1094</v>
       </c>
       <c r="I364" s="1" t="s">
-        <v>3667</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.2">
@@ -19177,10 +19186,10 @@
         <v>1183</v>
       </c>
       <c r="I403" s="1" t="s">
-        <v>3639</v>
+        <v>3633</v>
       </c>
       <c r="J403" t="s">
-        <v>3659</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.2">
@@ -20172,10 +20181,10 @@
         <v>1321</v>
       </c>
       <c r="I467" s="1" t="s">
-        <v>3640</v>
+        <v>3634</v>
       </c>
       <c r="J467" t="s">
-        <v>3662</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.2">
@@ -20536,10 +20545,10 @@
         <v>1375</v>
       </c>
       <c r="I490" s="1" t="s">
-        <v>3641</v>
+        <v>3635</v>
       </c>
       <c r="J490" t="s">
-        <v>3659</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.2">
@@ -21128,7 +21137,7 @@
         <v>3550</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>3605</v>
+        <v>3599</v>
       </c>
       <c r="E528" s="1" t="s">
         <v>1459</v>
@@ -21151,7 +21160,7 @@
         <v>3550</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>3605</v>
+        <v>3599</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>1463</v>
@@ -21171,7 +21180,7 @@
         <v>3550</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>3605</v>
+        <v>3599</v>
       </c>
       <c r="H530" s="1" t="s">
         <v>1467</v>
@@ -21185,7 +21194,7 @@
         <v>3550</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>3605</v>
+        <v>3599</v>
       </c>
       <c r="G531" s="1" t="s">
         <v>1469</v>
@@ -21213,7 +21222,7 @@
         <v>3550</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>3606</v>
+        <v>3600</v>
       </c>
       <c r="H533" s="1" t="s">
         <v>1472</v>
@@ -21227,13 +21236,13 @@
         <v>3550</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>3606</v>
+        <v>3600</v>
       </c>
       <c r="H534" s="1" t="s">
         <v>1474</v>
       </c>
       <c r="I534" s="1" t="s">
-        <v>3642</v>
+        <v>3636</v>
       </c>
     </row>
     <row r="535" spans="1:9" x14ac:dyDescent="0.2">
@@ -21241,7 +21250,7 @@
         <v>3550</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>3606</v>
+        <v>3600</v>
       </c>
       <c r="H535" s="1" t="s">
         <v>1475</v>
@@ -21803,10 +21812,10 @@
         <v>1578</v>
       </c>
       <c r="I564" s="1" t="s">
-        <v>3643</v>
+        <v>3637</v>
       </c>
       <c r="J564" t="s">
-        <v>3659</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="565" spans="1:10" x14ac:dyDescent="0.2">
@@ -21823,10 +21832,10 @@
         <v>1580</v>
       </c>
       <c r="I565" s="1" t="s">
-        <v>3644</v>
+        <v>3638</v>
       </c>
       <c r="J565" t="s">
-        <v>3659</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="566" spans="1:10" x14ac:dyDescent="0.2">
@@ -26661,10 +26670,10 @@
         <v>2352</v>
       </c>
       <c r="I855" s="1" t="s">
-        <v>3645</v>
+        <v>3639</v>
       </c>
       <c r="J855" t="s">
-        <v>3663</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="856" spans="1:10" x14ac:dyDescent="0.2">
@@ -26919,7 +26928,7 @@
         <v>2382</v>
       </c>
       <c r="I873" s="1" t="s">
-        <v>3646</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="874" spans="1:9" x14ac:dyDescent="0.2">
@@ -27684,7 +27693,7 @@
         <v>2478</v>
       </c>
       <c r="I927" s="1" t="s">
-        <v>3647</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="928" spans="1:9" x14ac:dyDescent="0.2">
@@ -27981,7 +27990,7 @@
         <v>2519</v>
       </c>
       <c r="I948" s="1" t="s">
-        <v>3648</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="949" spans="1:9" x14ac:dyDescent="0.2">
@@ -28240,7 +28249,7 @@
         <v>2558</v>
       </c>
       <c r="I965" s="1" t="s">
-        <v>3649</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="966" spans="1:9" x14ac:dyDescent="0.2">
@@ -28747,10 +28756,10 @@
         <v>2628</v>
       </c>
       <c r="I998" s="1" t="s">
-        <v>3650</v>
+        <v>3644</v>
       </c>
       <c r="J998" t="s">
-        <v>3659</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="999" spans="1:10" x14ac:dyDescent="0.2">
@@ -30520,10 +30529,10 @@
         <v>2877</v>
       </c>
       <c r="I1112" s="1" t="s">
-        <v>3651</v>
+        <v>3645</v>
       </c>
       <c r="J1112" t="s">
-        <v>3664</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="1113" spans="1:10" x14ac:dyDescent="0.2">
@@ -31009,10 +31018,10 @@
         <v>2946</v>
       </c>
       <c r="I1142" s="1" t="s">
-        <v>3652</v>
+        <v>3646</v>
       </c>
       <c r="J1142" t="s">
-        <v>3666</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="1143" spans="1:10" x14ac:dyDescent="0.2">
@@ -31043,10 +31052,10 @@
         <v>2949</v>
       </c>
       <c r="I1144" s="1" t="s">
-        <v>3653</v>
+        <v>3647</v>
       </c>
       <c r="J1144" t="s">
-        <v>3666</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="1145" spans="1:10" x14ac:dyDescent="0.2">
@@ -31083,10 +31092,10 @@
         <v>2954</v>
       </c>
       <c r="I1146" s="1" t="s">
-        <v>3654</v>
+        <v>3648</v>
       </c>
       <c r="J1146" t="s">
-        <v>3666</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="1147" spans="1:10" x14ac:dyDescent="0.2">
@@ -31194,10 +31203,10 @@
         <v>2971</v>
       </c>
       <c r="I1152" s="1" t="s">
-        <v>3655</v>
+        <v>3649</v>
       </c>
       <c r="J1152" t="s">
-        <v>3666</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="1153" spans="1:9" x14ac:dyDescent="0.2">
@@ -31510,10 +31519,10 @@
         <v>3027</v>
       </c>
       <c r="I1169" s="1" t="s">
-        <v>3656</v>
+        <v>3650</v>
       </c>
       <c r="J1169" t="s">
-        <v>3666</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="1170" spans="1:10" x14ac:dyDescent="0.2">
@@ -32097,10 +32106,10 @@
         <v>3136</v>
       </c>
       <c r="I1200" s="1" t="s">
-        <v>3657</v>
+        <v>3651</v>
       </c>
       <c r="J1200" t="s">
-        <v>3666</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="1201" spans="1:9" x14ac:dyDescent="0.2">
